--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Facilities" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Facilities'!$A$1:$G$264</definedName>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 27 Oct 2026, 14:58</t>
+          <t>Updated 28 Oct 2026, 10:27</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 28 Oct 2026, 10:27</t>
+          <t>Updated 28 Oct 2026, 17:37</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1049,7 +1049,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Health Post Ajegunle</t>
+          <t>General Hospital Orile Agege</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Papa Ashafa Health Post</t>
+          <t>Health Post Ajegunle</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iloro</t>
+          <t>Papa Ashafa Health Post</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary Health Centre Kwakwa Uku</t>
+          <t>Primary Health Centre Iloro</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Primary Health Centre Odunbakun</t>
+          <t>Primary Health Centre Kwakwa Uku</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primary Health Centre Powerline</t>
+          <t>Primary Health Centre Odunbakun</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sango (Lagos)</t>
+          <t>Primary Health Centre Powerline</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primary health centre Ibijoke Claudia Sanwoolu</t>
+          <t>Primary Health Centre Sango (Lagos)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ajeromi Ifelodun</t>
+          <t>Agege</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Asiwaju Bola Ahmed Tinubu Comprehensive centre</t>
+          <t>Primary health centre Ibijoke Claudia Sanwoolu</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1274,7 +1274,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>General Hospital Ajeromi</t>
+          <t>Asiwaju Bola Ahmed Tinubu Comprehensive centre</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Health Centre Akere</t>
+          <t>General Hospital Ajeromi</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajegunle</t>
+          <t>Health Centre Akere</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primary Health Centre Amukoko</t>
+          <t>Primary Health Centre Ajegunle</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibafon</t>
+          <t>Primary Health Centre Amukoko</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primary Health Centre Layeni</t>
+          <t>Primary Health Centre Ibafon</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oridilu</t>
+          <t>Primary Health Centre Layeni</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Primary Health Centre Tolu</t>
+          <t>Primary Health Centre Oridilu</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1474,17 +1474,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alimosho</t>
+          <t>Ajeromi Ifelodun</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ishuti Health Post</t>
+          <t>Primary Health Centre Tolu</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primary Health Centre Abaranje</t>
+          <t>Ishuti Health Post</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1524,7 +1524,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Primary Health Centre Aboru</t>
+          <t>Primary Health Centre Abaranje</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agodo</t>
+          <t>Primary Health Centre Aboru</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primary Health Centre Akowonjo</t>
+          <t>Primary Health Centre Agodo</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primary Health Centre Amikanle</t>
+          <t>Primary Health Centre Akowonjo</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ayobo</t>
+          <t>Primary Health Centre Amikanle</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primary Health Centre Bada</t>
+          <t>Primary Health Centre Ayobo</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Primary Health Centre Egan</t>
+          <t>Primary Health Centre Bada</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primary Health Centre Egbe Idimu (Helen Aderonke)</t>
+          <t>Primary Health Centre Egan</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijegun</t>
+          <t>Primary Health Centre Egbe Idimu (Helen Aderonke)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikola</t>
+          <t>Primary Health Centre Ijegun</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikotun</t>
+          <t>Primary Health Centre Ikola</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ipaja</t>
+          <t>Primary Health Centre Ikotun</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isefun</t>
+          <t>Primary Health Centre Ipaja</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isheri Olofin</t>
+          <t>Primary Health Centre Isefun</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isheri-Oshun</t>
+          <t>Primary Health Centre Isheri Olofin</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Primary Health Centre Meiran</t>
+          <t>Primary Health Centre Isheri-Oshun</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke-Odo</t>
+          <t>Primary Health Centre Meiran</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Primary Health Centre Olota</t>
+          <t>Primary Health Centre Oke-Odo</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Primary Health Centre Opeki</t>
+          <t>Primary Health Centre Olota</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Primary Health Centre Orisunbare</t>
+          <t>Primary Health Centre Opeki</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2024,7 +2024,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Primary Health Centre Rauf Aregbesola</t>
+          <t>Primary Health Centre Orisunbare</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2049,7 +2049,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Primary Health Centre Surulere</t>
+          <t>Primary Health Centre Rauf Aregbesola</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2074,17 +2074,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amuwo Odofin</t>
+          <t>Alimosho</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Health Post Irede</t>
+          <t>Primary Health Centre Surulere</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Health Post Tomaro</t>
+          <t>Health Post Irede</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Maternal And Child Health Centre Amuwo</t>
+          <t>Health Post Tomaro</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nigerian Navy Reference Hospital Ojo</t>
+          <t>Maternal And Child Health Centre Amuwo</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agboju</t>
+          <t>Nigerian Navy Reference Hospital Ojo</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2199,7 +2199,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Primary Health Centre Bola Ahmed Tinubu</t>
+          <t>Primary Health Centre Agboju</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2224,7 +2224,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Primary Health Centre Festac</t>
+          <t>Primary Health Centre Bola Ahmed Tinubu</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2249,7 +2249,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibeshe Amuwo Odofin</t>
+          <t>Primary Health Centre Festac</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2274,7 +2274,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbologun</t>
+          <t>Primary Health Centre Ibeshe Amuwo Odofin</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijegun</t>
+          <t>Primary Health Centre Igbologun</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2324,7 +2324,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Primary Health Centre Kirikiri</t>
+          <t>Primary Health Centre Ijegun</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2349,7 +2349,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Primary Health Centre Mile 2</t>
+          <t>Primary Health Centre Kirikiri</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sagbokoji</t>
+          <t>Primary Health Centre Mile 2</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Primary Health Centre Satellite</t>
+          <t>Primary Health Centre Sagbokoji</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2424,17 +2424,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apapa</t>
+          <t>Amuwo Odofin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijora</t>
+          <t>Primary Health Centre Satellite</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Primary Health Centre Marine Beach</t>
+          <t>Primary Health Centre Ijora</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Primary Health Centre Nanti</t>
+          <t>Primary Health Centre Marine Beach</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ojora Olugbode</t>
+          <t>Primary Health Centre Nanti</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2524,7 +2524,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Primary Health Centre Olojowon</t>
+          <t>Primary Health Centre Ojora Olugbode</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2549,7 +2549,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oluwole</t>
+          <t>Primary Health Centre Olojowon</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sari Iganmu</t>
+          <t>Primary Health Centre Oluwole</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Primary Health Centre Zion</t>
+          <t>Primary Health Centre Sari Iganmu</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2624,17 +2624,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Badagry</t>
+          <t>Apapa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>General Hospital Badagry</t>
+          <t>Primary Health Centre Zion</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Health Post Isamole</t>
+          <t>General Hospital Badagry</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajara</t>
+          <t>Health Post Isamole</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Primary Health Centre Apa Badagry</t>
+          <t>Primary Health Centre Ajara</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Primary Health Centre Araromi</t>
+          <t>Primary Health Centre Apa Badagry</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2749,7 +2749,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Primary Health Centre Farasime</t>
+          <t>Primary Health Centre Araromi</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2774,7 +2774,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibereko Barracks</t>
+          <t>Primary Health Centre Farasime</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbogbele</t>
+          <t>Primary Health Centre Ibereko Barracks</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -2824,7 +2824,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ilado</t>
+          <t>Primary Health Centre Igbogbele</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ilogbo</t>
+          <t>Primary Health Centre Ilado</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2874,7 +2874,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Primary Health Centre Marina</t>
+          <t>Primary Health Centre Ilogbo</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Primary Health Centre Morogbo</t>
+          <t>Primary Health Centre Marina</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -2924,7 +2924,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Primary Health Centre Mowo</t>
+          <t>Primary Health Centre Morogbo</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Primary Health Centre Pota</t>
+          <t>Primary Health Centre Mowo</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sakpo</t>
+          <t>Primary Health Centre Pota</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Primary Health Centre Seme</t>
+          <t>Primary Health Centre Sakpo</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3024,17 +3024,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Epe</t>
+          <t>Badagry</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>General Hospital Agbowa</t>
+          <t>Primary Health Centre Seme</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>General Hospital Epe</t>
+          <t>General Hospital Agbowa</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Primary Health Centre Eredo</t>
+          <t>General Hospital Epe</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Primary Health Centre Odomola</t>
+          <t>Primary Health Centre Eredo</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3124,7 +3124,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Primary Health Centre Papa</t>
+          <t>Primary Health Centre Odomola</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Primary Health Centre Poka</t>
+          <t>Primary Health Centre Papa</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3174,17 +3174,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eti Osa</t>
+          <t>Epe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Maternal and Child health Centre Eti-Osa</t>
+          <t>Primary Health Centre Poka</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Police Hospital Falomo</t>
+          <t>Maternal and Child health Centre Eti-Osa</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ado Langbasa</t>
+          <t>Police Hospital Falomo</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajah</t>
+          <t>Primary Health Centre Ado Langbasa</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3274,7 +3274,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajiran</t>
+          <t>Primary Health Centre Ajah</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3299,7 +3299,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Primary Health Centre Badore</t>
+          <t>Primary Health Centre Ajiran</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbo-Efon</t>
+          <t>Primary Health Centre Badore</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikota</t>
+          <t>Primary Health Centre Igbo-Efon</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -3374,7 +3374,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikoyi</t>
+          <t>Primary Health Centre Ikota</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -3399,7 +3399,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ilasan</t>
+          <t>Primary Health Centre Ikoyi</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -3424,7 +3424,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Primary Health Centre Obalende</t>
+          <t>Primary Health Centre Ilasan</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -3449,7 +3449,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ogombo</t>
+          <t>Primary Health Centre Obalende</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oniru</t>
+          <t>Primary Health Centre Ogombo</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sangotedo</t>
+          <t>Primary Health Centre Oniru</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Primary health centre Ifesowapo</t>
+          <t>Primary Health Centre Sangotedo</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -3549,17 +3549,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ibeju Lekki</t>
+          <t>Eti Osa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Primary Health Centre Apakin</t>
+          <t>Primary health centre Ifesowapo</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Primary Health Centre Awoyaya 1</t>
+          <t>Primary Health Centre Apakin</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -3599,7 +3599,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Primary Health Centre Bogije</t>
+          <t>Primary Health Centre Awoyaya 1</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -3624,7 +3624,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Primary Health Centre Folu</t>
+          <t>Primary Health Centre Bogije</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibeju</t>
+          <t>Primary Health Centre Folu</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iberekodo</t>
+          <t>Primary Health Centre Ibeju</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Primary Health Centre Idasho</t>
+          <t>Primary Health Centre Iberekodo</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -3724,7 +3724,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Primary Health Centre Lakowe</t>
+          <t>Primary Health Centre Idasho</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Primary Health Centre Lekki</t>
+          <t>Primary Health Centre Lakowe</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Primary Health Centre Okunraye</t>
+          <t>Primary Health Centre Lekki</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Primary Health Centre Orimedu</t>
+          <t>Primary Health Centre Okunraye</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -3824,7 +3824,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Primary Health Centre Otunla</t>
+          <t>Primary Health Centre Orimedu</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -3849,7 +3849,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Primary Health Centre Solu Alade</t>
+          <t>Primary Health Centre Otunla</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -3874,17 +3874,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ifako Ijaye</t>
+          <t>Ibeju Lekki</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>General Hospital Ifako Ijaiye</t>
+          <t>Primary Health Centre Solu Alade</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -3899,7 +3899,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Primary Health Centre Abule Tuntun</t>
+          <t>General Hospital Ifako Ijaiye</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -3924,7 +3924,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Primary Health Centre Adesola</t>
+          <t>Primary Health Centre Abule Tuntun</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agbado (Primary Health Centre Kola)</t>
+          <t>Primary Health Centre Adesola</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ifako</t>
+          <t>Primary Health Centre Agbado (Primary Health Centre Kola)</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iju</t>
+          <t>Primary Health Centre Ifako</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ilo Ajegunle</t>
+          <t>Primary Health Centre Iju</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -4049,7 +4049,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isokan</t>
+          <t>Primary Health Centre Ilo Ajegunle</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -4074,7 +4074,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Primary Health Centre Obawole</t>
+          <t>Primary Health Centre Isokan</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ogundinmu</t>
+          <t>Primary Health Centre Obawole</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -4124,17 +4124,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ikeja</t>
+          <t>Ifako Ijaye</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Health Post Alade Market</t>
+          <t>Primary Health Centre Ogundinmu</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lagos State University Teaching Hospital Ikeja</t>
+          <t>Health Post Alade Market</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Primary Health Center Agidingbi</t>
+          <t>Lagos State University Teaching Hospital Ikeja</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Primary Health Centre Abule Onigbagbo</t>
+          <t>Primary Health Center Agidingbi</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -4224,7 +4224,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Primary Health Centre Aguda</t>
+          <t>Primary Health Centre Abule Onigbagbo</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Primary Health Centre Akiode</t>
+          <t>Primary Health Centre Aguda</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -4274,7 +4274,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Primary Health Centre Alausa</t>
+          <t>Primary Health Centre Akiode</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Primary Health Centre Beko Ransome-Kuti</t>
+          <t>Primary Health Centre Alausa</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -4324,7 +4324,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikeja</t>
+          <t>Primary Health Centre Beko Ransome-Kuti</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -4349,7 +4349,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ogba Oluwole</t>
+          <t>Primary Health Centre Ikeja</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ojodu</t>
+          <t>Primary Health Centre Ogba Oluwole</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke Ira Mdg</t>
+          <t>Primary Health Centre Ojodu</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -4424,7 +4424,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke-Ira Powerline</t>
+          <t>Primary Health Centre Oke Ira Mdg</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Primary Health Centre Onigbongbo</t>
+          <t>Primary Health Centre Oke-Ira Powerline</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -4474,7 +4474,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Primary Health Centre Onilekere</t>
+          <t>Primary Health Centre Onigbongbo</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Primary Health Centre Onipetesi</t>
+          <t>Primary Health Centre Onilekere</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Primary Health Centre Opebi</t>
+          <t>Primary Health Centre Onipetesi</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -4549,7 +4549,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oregun</t>
+          <t>Primary Health Centre Opebi</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Primary Health Centre Wasimi</t>
+          <t>Primary Health Centre Oregun</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -4599,17 +4599,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ikorodu</t>
+          <t>Ikeja</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Eocc</t>
+          <t>Primary Health Centre Wasimi</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>General Hospital Ikorodu</t>
+          <t>Eocc</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -4649,7 +4649,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>General Hospital Imota</t>
+          <t>General Hospital Ikorodu</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -4674,7 +4674,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Health Centre Ijede</t>
+          <t>General Hospital Imota</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -4699,7 +4699,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Health Post Parafa</t>
+          <t>Health Centre Ijede</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -4724,7 +4724,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Primary Health Centre (Imota) Orio Kuta</t>
+          <t>Health Post Parafa</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -4749,7 +4749,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agbede</t>
+          <t>Primary Health Centre (Imota) Orio Kuta</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -4774,7 +4774,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agbele</t>
+          <t>Primary Health Centre Agbede</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -4799,7 +4799,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agura</t>
+          <t>Primary Health Centre Agbele</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -4824,7 +4824,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Primary Health Centre Bayeku</t>
+          <t>Primary Health Centre Agura</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Primary Health Centre Erunwen</t>
+          <t>Primary Health Centre Bayeku</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ewu Elepe</t>
+          <t>Primary Health Centre Erunwen</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -4899,7 +4899,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibeshe</t>
+          <t>Primary Health Centre Ewu Elepe</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -4924,7 +4924,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbalu</t>
+          <t>Primary Health Centre Ibeshe</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -4949,7 +4949,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbogbo (Primary Health Centreagbele)</t>
+          <t>Primary Health Centre Igbalu</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igboolomu</t>
+          <t>Primary Health Centre Igbogbo (Primary Health Centreagbele)</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ipakodo</t>
+          <t>Primary Health Centre Igboolomu</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isiu</t>
+          <t>Primary Health Centre Ipakodo</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ita-Elewa</t>
+          <t>Primary Health Centre Isiu</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Primary Health Centre Lasunwo</t>
+          <t>Primary Health Centre Ita-Elewa</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Primary Health Centre Losi Oba</t>
+          <t>Primary Health Centre Lasunwo</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -5124,7 +5124,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Primary Health Centre Majidun</t>
+          <t>Primary Health Centre Losi Oba</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -5149,7 +5149,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Primary Health Centre Odonla</t>
+          <t>Primary Health Centre Majidun</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
@@ -5174,7 +5174,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Primary Health Centre Offin</t>
+          <t>Primary Health Centre Odonla</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke Eletu</t>
+          <t>Primary Health Centre Offin</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke-Lisa</t>
+          <t>Primary Health Centre Oke Eletu</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Primary Health Centre Olorunda</t>
+          <t>Primary Health Centre Oke-Lisa</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ori Okuta</t>
+          <t>Primary Health Centre Olorunda</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
@@ -5299,17 +5299,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kosofe</t>
+          <t>Ikorodu</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>General Hospital Gbagada</t>
+          <t>Primary Health Centre Ori Okuta</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
@@ -5324,7 +5324,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agboyi</t>
+          <t>General Hospital Gbagada</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
@@ -5349,7 +5349,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Primary Health Centre Alapere</t>
+          <t>Primary Health Centre Agboyi</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Primary Health Centre Idera</t>
+          <t>Primary Health Centre Alapere</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
@@ -5399,7 +5399,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ikosi</t>
+          <t>Primary Health Centre Idera</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ketu (Mascara)</t>
+          <t>Primary Health Centre Ikosi</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>241</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Primary Health Centre Maidan</t>
+          <t>Primary Health Centre Ketu (Mascara)</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -5474,7 +5474,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Primary Health Centre Mende</t>
+          <t>Primary Health Centre Maidan</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ogudu Kosofe</t>
+          <t>Primary Health Centre Mende</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>244</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Primary Health Centre Olowora</t>
+          <t>Primary Health Centre Ogudu Kosofe</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oworo</t>
+          <t>Primary Health Centre Olowora</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
@@ -5574,17 +5574,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lagos Island</t>
+          <t>Kosofe</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Anikantamo Primary Health Centre</t>
+          <t>Primary Health Centre Oworo</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
@@ -5599,7 +5599,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Carena Health Post</t>
+          <t>Anikantamo Primary Health Centre</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -5624,7 +5624,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Health Post Itafaji</t>
+          <t>Carena Health Post</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
@@ -5649,7 +5649,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Health Post Tajudeen Olusi</t>
+          <t>Health Post Itafaji</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Lagos Island Maternity Hospital</t>
+          <t>Health Post Tajudeen Olusi</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Massey Street Children Hospital</t>
+          <t>Lagos Island Maternity Hospital</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Onala Health Post</t>
+          <t>Massey Street Children Hospital</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Primary Health Centre Agarawu (Oko Awo)</t>
+          <t>Onala Health Post</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Primary Health Centre Araromi</t>
+          <t>Primary Health Centre Agarawu (Oko Awo)</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
@@ -5799,7 +5799,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iga Iduganrun</t>
+          <t>Primary Health Centre Araromi</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oba Adeyinka Oyekan</t>
+          <t>Primary Health Centre Iga Iduganrun</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
@@ -5849,7 +5849,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Primary Health Centre Olowogbowo</t>
+          <t>Primary Health Centre Oba Adeyinka Oyekan</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
@@ -5874,7 +5874,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>260</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Primary Health Centre Phase 3</t>
+          <t>Primary Health Centre Olowogbowo</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
@@ -5899,7 +5899,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Primary Health Centre Sura</t>
+          <t>Primary Health Centre Phase 3</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
@@ -5924,17 +5924,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lagos Mainland</t>
+          <t>Lagos Island</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Federal Medical Centre Ebute-Metta</t>
+          <t>Primary Health Centre Sura</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
@@ -5949,7 +5949,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Health Centre Harvey Road</t>
+          <t>Federal Medical Centre Ebute-Metta</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
@@ -5974,7 +5974,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>265</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Primary Health Centre Aiyetoro</t>
+          <t>Health Centre Harvey Road</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -5999,7 +5999,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iwaya</t>
+          <t>Primary Health Centre Aiyetoro</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
@@ -6024,7 +6024,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Primary Health Centre Otto</t>
+          <t>Primary Health Centre Iwaya</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
@@ -6049,7 +6049,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Primary Health Centre Simpson</t>
+          <t>Primary Health Centre Otto</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
@@ -6074,17 +6074,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mushin</t>
+          <t>Lagos Mainland</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Idi- Araba Health Post</t>
+          <t>Primary Health Centre Simpson</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (Luth) 2</t>
+          <t>Idi- Araba Health Post</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (Luth) Clinic</t>
+          <t>Lagos University Teaching Hospital (Luth) 2</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajeabo</t>
+          <t>Lagos University Teaching Hospital (Luth) Clinic</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ajisegiri</t>
+          <t>Primary Health Centre Ajeabo</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Primary Health Centre Alves</t>
+          <t>Primary Health Centre Ajisegiri</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
@@ -6224,7 +6224,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Primary Health Centre Anikulapo</t>
+          <t>Primary Health Centre Alves</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -6249,7 +6249,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ayantuga</t>
+          <t>Primary Health Centre Anikulapo</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -6274,7 +6274,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>285</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Primary Health Centre Coker</t>
+          <t>Primary Health Centre Ayantuga</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbo Owu</t>
+          <t>Primary Health Centre Coker</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -6324,7 +6324,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Primary Health Centre Isolo</t>
+          <t>Primary Health Centre Igbo Owu</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -6349,7 +6349,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Primary Health Centre Itire Ijesha</t>
+          <t>Primary Health Centre Isolo</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Primary Health Centre Kajola</t>
+          <t>Primary Health Centre Itire Ijesha</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Primary Health Centre Palm Avenue</t>
+          <t>Primary Health Centre Kajola</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
@@ -6424,17 +6424,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>291</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Mushin</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Health Centre Shibiri</t>
+          <t>Primary Health Centre Palm Avenue</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
@@ -6449,7 +6449,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Primary Health Centre Afromedia</t>
+          <t>Health Centre Shibiri</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -6474,7 +6474,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Primary Health Centre Era Mini</t>
+          <t>Primary Health Centre Afromedia</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
@@ -6499,7 +6499,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iba</t>
+          <t>Primary Health Centre Era Mini</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Primary Health Centre Igbede</t>
+          <t>Primary Health Centre Iba</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -6549,7 +6549,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>298</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijagemo</t>
+          <t>Primary Health Centre Igbede</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijanikin</t>
+          <t>Primary Health Centre Ijagemo</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ijedodo</t>
+          <t>Primary Health Centre Ijanikin</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -6624,7 +6624,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Primary Health Centre Imude</t>
+          <t>Primary Health Centre Ijedodo</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -6649,7 +6649,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Primary Health Centre Irewe</t>
+          <t>Primary Health Centre Imude</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -6674,7 +6674,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ishashi</t>
+          <t>Primary Health Centre Irewe</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
@@ -6699,7 +6699,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>305</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oba Adeshina</t>
+          <t>Primary Health Centre Ishashi</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -6724,7 +6724,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ojo</t>
+          <t>Primary Health Centre Oba Adeshina</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oke-Ijeun</t>
+          <t>Primary Health Centre Ojo</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
@@ -6774,7 +6774,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Primary Health Centre Okokomaiko</t>
+          <t>Primary Health Centre Oke-Ijeun</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
@@ -6799,17 +6799,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Oshodi Isolo</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Dauda Ilo</t>
+          <t>Primary Health Centre Okokomaiko</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>General Hospital Isolo</t>
+          <t>Dauda Ilo</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ailegun</t>
+          <t>General Hospital Isolo</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
@@ -6874,7 +6874,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ayo Ni</t>
+          <t>Primary Health Centre Ailegun</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ewetuntun</t>
+          <t>Primary Health Centre Ayo Ni</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
@@ -6924,7 +6924,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ilasa</t>
+          <t>Primary Health Centre Ewetuntun</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
@@ -6949,7 +6949,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ishaga</t>
+          <t>Primary Health Centre Ilasa</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
@@ -6974,7 +6974,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iyana Ejigbo</t>
+          <t>Primary Health Centre Ishaga</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
@@ -6999,7 +6999,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Primary Health Centre Jakande</t>
+          <t>Primary Health Centre Iyana Ejigbo</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Primary Health Centre Lsdpc</t>
+          <t>Primary Health Centre Jakande</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Primary Health Centre Mafoluku</t>
+          <t>Primary Health Centre Lsdpc</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -7074,7 +7074,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ona Iwamimo</t>
+          <t>Primary Health Centre Mafoluku</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oshodi</t>
+          <t>Primary Health Centre Ona Iwamimo</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -7124,17 +7124,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Shomolu</t>
+          <t>Oshodi Isolo</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>General Hospital Somolu</t>
+          <t>Primary Health Centre Oshodi</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Primary Health Centre Akinwumi Ambode</t>
+          <t>General Hospital Somolu</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -7174,7 +7174,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Primary Health Centre Akoka</t>
+          <t>Primary Health Centre Akinwumi Ambode</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ashogbon</t>
+          <t>Primary Health Centre Akoka</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Primary Health Centre Cms</t>
+          <t>Primary Health Centre Ashogbon</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ibijoke Sanwoolu</t>
+          <t>Primary Health Centre Cms</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Primary Health Centre Mafowoku</t>
+          <t>Primary Health Centre Ibijoke Sanwoolu</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
@@ -7299,7 +7299,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Primary Health Centre Oloja (Late Hon Adewale Awokoya PHC))</t>
+          <t>Primary Health Centre Mafowoku</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -7324,7 +7324,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Primary Health Centre Wright</t>
+          <t>Primary Health Centre Oloja (Late Hon Adewale Awokoya PHC))</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -7349,17 +7349,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Surulere</t>
+          <t>Shomolu</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Primary Health Centre Airways</t>
+          <t>Primary Health Centre Wright</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
@@ -7374,7 +7374,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Primary Health Centre Akerele</t>
+          <t>Primary Health Centre Airways</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
@@ -7399,7 +7399,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Primary Health Centre Anjorin</t>
+          <t>Primary Health Centre Akerele</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Primary Health Centre Coker Aguda</t>
+          <t>Primary Health Centre Anjorin</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
@@ -7449,7 +7449,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Primary Health Centre Ejire</t>
+          <t>Primary Health Centre Coker Aguda</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -7474,7 +7474,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Primary Health Centre Femi Gbajabiamila</t>
+          <t>Primary Health Centre Ejire</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -7499,7 +7499,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Primary Health Centre Iponri</t>
+          <t>Primary Health Centre Femi Gbajabiamila</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Primary Health Centre Orile Coker</t>
+          <t>Primary Health Centre Iponri</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
@@ -7549,7 +7549,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Rgh Mcc Gbaja</t>
+          <t>Primary Health Centre Orile Coker</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
@@ -7574,42 +7574,32 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Agege</t>
+          <t>Surulere</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Agege - Promise Medical Centre</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>Receipt confirmed by facility</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="F263" t="n">
-        <v>20529</v>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>20,529 m from facility</t>
-        </is>
-      </c>
+          <t>Rgh Mcc Gbaja</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>Not reported yet</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7619,7 +7609,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>General Hospital Orile Agege</t>
+          <t>Agege - Promise Medical Centre</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -7629,15 +7619,15 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>22959</v>
+        <v>23159</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>22,959 m from facility</t>
+          <t>23,159 m from facility; reason given (see KoBo)</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 28 Oct 2026, 17:37</t>
+          <t>Updated 28 Oct 2026, 22:38</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 28 Oct 2026, 22:38</t>
+          <t>Updated 29 Oct 2026, 02:47</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 29 Oct 2026, 02:47</t>
+          <t>Updated 29 Oct 2026, 09:26</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 29 Oct 2026, 09:26</t>
+          <t>Updated 29 Oct 2026, 17:06</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 29 Oct 2026, 17:06</t>
+          <t>Updated 29 Oct 2026, 22:06</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 29 Oct 2026, 22:06</t>
+          <t>Updated 30 Oct 2026, 01:57</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 30 Oct 2026, 01:57</t>
+          <t>Updated 30 Oct 2026, 08:04</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 30 Oct 2026, 08:04</t>
+          <t>Updated 30 Oct 2026, 15:06</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 30 Oct 2026, 15:06</t>
+          <t>Updated 30 Oct 2026, 20:20</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 30 Oct 2026, 20:20</t>
+          <t>Updated 31 Oct 2026, 00:44</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 31 Oct 2026, 00:44</t>
+          <t>Updated 31 Oct 2026, 06:36</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 31 Oct 2026, 06:36</t>
+          <t>Updated 31 Oct 2026, 13:23</t>
         </is>
       </c>
     </row>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 31 Oct 2026, 13:23</t>
+          <t>Updated 31 Oct 2026, 18:42</t>
         </is>
       </c>
     </row>
